--- a/data/trans_orig/IP2002-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2002-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12872</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>12670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26441</t>
+          <t>26884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116134</t>
+          <t>115962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>125112</t>
+          <t>124867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125847</t>
+          <t>126157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136506</t>
+          <t>136922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246072</t>
+          <t>245629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>259908</t>
+          <t>259843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21615</t>
+          <t>22649</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24690</t>
+          <t>24360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>24527</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42507</t>
+          <t>43393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>164169</t>
+          <t>163135</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175562</t>
+          <t>175085</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179532</t>
+          <t>179862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>191997</t>
+          <t>191971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>347500</t>
+          <t>346614</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>364070</t>
+          <t>365480</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17575</t>
+          <t>17981</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13737</t>
+          <t>13655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27188</t>
+          <t>26656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117422</t>
+          <t>118063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>126271</t>
+          <t>126434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121767</t>
+          <t>121361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132130</t>
+          <t>132042</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>242886</t>
+          <t>243418</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>256337</t>
+          <t>256419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22750</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>15232</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33056</t>
+          <t>33618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177212</t>
+          <t>176768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190257</t>
+          <t>190134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>182929</t>
+          <t>182720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192624</t>
+          <t>192495</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364414</t>
+          <t>363852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380144</t>
+          <t>379749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36410</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57038</t>
+          <t>58466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40380</t>
+          <t>40242</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>62884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80403</t>
+          <t>81343</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111998</t>
+          <t>110831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>588002</t>
+          <t>586574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>609418</t>
+          <t>608630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>623249</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>644643</t>
+          <t>644781</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1218065</t>
+          <t>1219232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1249660</t>
+          <t>1248720</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>12775</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>19653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27330</t>
+          <t>28207</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120900</t>
+          <t>120393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129559</t>
+          <t>129710</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>121566</t>
+          <t>121734</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>133754</t>
+          <t>133595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247225</t>
+          <t>246348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>261264</t>
+          <t>261652</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10409</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23300</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21783</t>
+          <t>21836</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23314</t>
+          <t>23214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40500</t>
+          <t>40886</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168219</t>
+          <t>168822</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>180918</t>
+          <t>181110</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>190970</t>
+          <t>190917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203296</t>
+          <t>202768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>363772</t>
+          <t>363386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>380958</t>
+          <t>381058</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7086</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>17956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>14790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29561</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129440</t>
+          <t>129323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139300</t>
+          <t>139317</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>133951</t>
+          <t>134337</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145207</t>
+          <t>145376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>267390</t>
+          <t>268148</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282552</t>
+          <t>282161</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16927</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22143</t>
+          <t>22526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183573</t>
+          <t>183484</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>191797</t>
+          <t>191798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179339</t>
+          <t>180148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>190834</t>
+          <t>191163</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>367670</t>
+          <t>367287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381112</t>
+          <t>380940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27367</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47763</t>
+          <t>47592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38044</t>
+          <t>38542</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60920</t>
+          <t>60200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71459</t>
+          <t>71872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101364</t>
+          <t>103048</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>615128</t>
+          <t>615299</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>635524</t>
+          <t>634532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>641779</t>
+          <t>642499</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>664655</t>
+          <t>664157</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1264227</t>
+          <t>1262543</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1294132</t>
+          <t>1293719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12505</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2513</t>
+          <t>2170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11053</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112164</t>
+          <t>112103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121212</t>
+          <t>121337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>128057</t>
+          <t>128274</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136597</t>
+          <t>136940</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>243290</t>
+          <t>244664</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256372</t>
+          <t>256203</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9388</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7519</t>
+          <t>7268</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>18176</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34333</t>
+          <t>34364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172650</t>
+          <t>173315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184124</t>
+          <t>184516</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>192090</t>
+          <t>192501</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>203158</t>
+          <t>203409</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>369856</t>
+          <t>369825</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>385023</t>
+          <t>385475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10697</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6773</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>137861</t>
+          <t>137470</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>145380</t>
+          <t>145593</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149487</t>
+          <t>149480</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157601</t>
+          <t>157800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290239</t>
+          <t>290802</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301821</t>
+          <t>301923</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22286</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17631</t>
+          <t>17393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>18175</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34082</t>
+          <t>35245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170197</t>
+          <t>170643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183571</t>
+          <t>183672</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>173050</t>
+          <t>173288</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>184509</t>
+          <t>184442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>349081</t>
+          <t>347918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>365666</t>
+          <t>364988</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>31165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>52486</t>
+          <t>52117</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45040</t>
+          <t>44593</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61774</t>
+          <t>61321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90001</t>
+          <t>89220</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>606345</t>
+          <t>606714</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>627430</t>
+          <t>627666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>655855</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>674742</t>
+          <t>675609</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1269725</t>
+          <t>1270506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1297952</t>
+          <t>1298405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,7 +6624,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>104954</t>
+          <t>104978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112384</t>
+          <t>112464</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127493</t>
+          <t>127492</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134735</t>
+          <t>134802</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235417</t>
+          <t>235160</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246013</t>
+          <t>245773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21521</t>
+          <t>22211</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>20780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37271</t>
+          <t>37366</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165377</t>
+          <t>164687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178665</t>
+          <t>178220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228911</t>
+          <t>228362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>242012</t>
+          <t>241359</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>398769</t>
+          <t>398674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>417393</t>
+          <t>417580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>15686</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22273</t>
+          <t>21636</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13957</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34108</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172539</t>
+          <t>172301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183130</t>
+          <t>183559</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161430</t>
+          <t>162067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176177</t>
+          <t>176050</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>337582</t>
+          <t>339248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>357733</t>
+          <t>357292</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,13%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3420</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14379</t>
+          <t>13760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25546</t>
+          <t>26244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149004</t>
+          <t>149031</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160070</t>
+          <t>160177</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>163484</t>
+          <t>164103</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174254</t>
+          <t>174443</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>318433</t>
+          <t>317735</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>333008</t>
+          <t>332563</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>28474</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51005</t>
+          <t>50197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27882</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50173</t>
+          <t>49894</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62221</t>
+          <t>61602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93246</t>
+          <t>92702</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>605066</t>
+          <t>605874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>626842</t>
+          <t>627597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>697292</t>
+          <t>697571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>719583</t>
+          <t>720079</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1310290</t>
+          <t>1310834</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341315</t>
+          <t>1341934</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2002-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2002-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11203</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6383</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17394</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7395</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4139</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3726</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12464</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,73%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11203</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6585</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17350</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12670</t>
+          <t>12028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26884</t>
+          <t>25811</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>132304</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>126113</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>137124</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>121611</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>115962</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>124867</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>116542</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>125280</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,27%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>132304</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>126157</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>136922</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>245629</t>
+          <t>246702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>259843</t>
+          <t>260485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>143507</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>143507</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>143507</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>129006</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>129006</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>129006</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>143507</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>143507</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>143507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>11675</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25187</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,33%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>15327</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10699</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22649</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10379</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21753</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>17732</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12251</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>24360</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24527</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43393</t>
+          <t>41829</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>186490</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>179035</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>192547</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,67%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>170457</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>163135</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>175085</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>164031</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>175405</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>186490</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>179862</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>191971</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,32%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>346614</t>
+          <t>348178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>365480</t>
+          <t>365112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,62%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>204222</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>204222</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>204222</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185784</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>204222</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>204222</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>204222</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11566</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6726</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17368</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>7917</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4298</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12669</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4710</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13245</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11566</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7300</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17981</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13655</t>
+          <t>13883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26656</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,11%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>127776</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>121974</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>132616</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,7%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>122815</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>118063</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>126434</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>117487</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>126022</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,94%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>127776</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>121361</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>132042</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>243418</t>
+          <t>242761</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>256419</t>
+          <t>256191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139342</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139342</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139342</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>130732</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>130732</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>130732</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139342</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139342</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139342</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9378</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14830</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>15182</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9384</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22750</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23274</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,61%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9378</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5457</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15232</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33618</t>
+          <t>33757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>188574</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>183122</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>192783</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>184336</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>176768</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>190134</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>176244</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>189614</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,39%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>188574</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>182720</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>192495</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>363852</t>
+          <t>363713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>379749</t>
+          <t>379932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>199518</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>199518</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>199518</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>197952</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>197952</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>197952</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>49879</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>40464</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>63034</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,2%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>45821</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>36410</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>58466</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35874</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>57442</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>49879</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>40242</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>62884</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81343</t>
+          <t>81953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110831</t>
+          <t>111232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>635144</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>621989</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>644559</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,8%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>895</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>599219</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>586574</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>608630</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>587598</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>609166</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,94%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>956</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>635144</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>622139</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>644781</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1219232</t>
+          <t>1218831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1248720</t>
+          <t>1248110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>685023</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>685023</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>685023</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>685023</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>685023</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>685023</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12656</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7829</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19395</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6665</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3458</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3463</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12714</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>12656</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7792</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19653</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>27099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>128731</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>121992</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>133558</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>126503</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>120393</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>129710</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>120454</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>129705</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,41%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,45%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>97,4%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>128731</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>121734</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>133595</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,05%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>86,1%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>94,49%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>348</t>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246348</t>
+          <t>247456</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>261652</t>
+          <t>261355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>141387</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>141387</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>141387</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133168</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>141387</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>141387</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>141387</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15044</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10053</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22328</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>16018</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10409</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22697</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10297</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>22770</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15044</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9985</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21836</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40886</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>197709</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>190425</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>202700</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>175501</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>168822</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>181110</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>168749</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>181222</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>197709</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>190917</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>202768</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,93%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>363386</t>
+          <t>363964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>381058</t>
+          <t>381464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212753</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212753</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212753</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>191519</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>191519</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>191519</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>308</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212753</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212753</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212753</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11569</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6999</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18300</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9307</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5341</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15335</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5191</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14758</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>11569</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>6917</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>17956</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,6%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14790</t>
+          <t>14735</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28803</t>
+          <t>28637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140724</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>133993</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145294</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,98%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>135351</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>129323</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>139317</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>129900</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>139467</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,57%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140724</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>134337</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>145376</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,4%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>268148</t>
+          <t>268314</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282161</t>
+          <t>282216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>152293</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>144658</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>152293</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9414</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16099</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4681</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1749</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10063</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2183</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9761</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9414</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5103</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16118</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,8%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8873</t>
+          <t>8511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>21972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>186852</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>180167</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>191425</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,8%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>188866</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>183484</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>191798</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>183786</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>191364</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,58%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>186852</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>180148</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>191163</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,2%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>367287</t>
+          <t>367841</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380940</t>
+          <t>381302</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,82%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>196266</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>196266</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>196266</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193547</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193547</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193547</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>196266</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>196266</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>196266</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>48684</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>37611</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>60864</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,93%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>36672</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28359</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47592</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>27318</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>46356</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,53%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>48684</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>38542</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>60200</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71872</t>
+          <t>71434</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103048</t>
+          <t>100916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>654015</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>641835</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>665088</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,07%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>901</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>626219</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>615299</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>634532</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>616535</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>635573</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,47%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,82%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>654015</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>642499</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>664157</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1262543</t>
+          <t>1264675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1293719</t>
+          <t>1294157</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>702699</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>702699</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>702699</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>702699</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>702699</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>702699</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2174</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10541</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6844</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3332</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12566</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3466</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12769</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,49%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5365</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2170</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10836</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19115</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>133745</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>128569</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>136936</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>92,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>117825</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>112103</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>121337</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>111900</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>121203</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,51%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>133745</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>128274</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>136940</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,14%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244664</t>
+          <t>244077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256203</t>
+          <t>256201</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>139110</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>124669</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>124669</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>124669</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>139110</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12131</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7312</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19309</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13902</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>20197</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9166</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20246</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,18%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12131</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7268</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18176</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34364</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>198546</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>191368</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>203365</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>179610</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>173315</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>184516</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>173266</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>184346</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>198546</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>192501</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>203409</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>369825</t>
+          <t>370373</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>385475</t>
+          <t>385743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>210677</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>210677</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>210677</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>310</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>193512</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>193512</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>193512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>210677</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>210677</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>210677</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5630</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2544</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10505</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5689</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2574</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10697</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2590</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9952</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>5630</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2627</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>10947</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>154797</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>149922</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157883</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>93,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>142478</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>137470</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>145593</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>138215</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>145577</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,16%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>154797</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>149480</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>157800</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>290802</t>
+          <t>290206</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301923</t>
+          <t>301967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>160427</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148167</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>160427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10590</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16738</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>14499</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8811</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>21840</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9337</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>21979</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,53%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10590</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>17393</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18175</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35245</t>
+          <t>34061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>180091</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>173943</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>184761</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,45%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,22%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>177984</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>170643</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>183672</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>170504</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>183146</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,47%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>180091</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>173288</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>184442</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,45%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>347918</t>
+          <t>349102</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>364988</t>
+          <t>365662</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>190681</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>192483</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>190681</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33716</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25408</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>43923</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>40933</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>31165</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>52117</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>31333</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>51664</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>6,21%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33716</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>25286</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>44593</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61321</t>
+          <t>61818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89220</t>
+          <t>89187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>667179</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>656972</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>675487</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>617898</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>606714</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>627666</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>607167</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>627498</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>93,79%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>667179</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>656302</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>675609</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1270506</t>
+          <t>1270539</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1298405</t>
+          <t>1297908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,45%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>988</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>658831</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>658831</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>658831</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4181</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8247</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5451</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2606</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10092</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>10856</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118698</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114632</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>121234</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>109619</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>104978</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>112464</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>132058</t>
+          <t>113497</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127492</t>
+          <t>108446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134802</t>
+          <t>116492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>241677</t>
+          <t>232195</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235160</t>
+          <t>226409</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>245773</t>
+          <t>236416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122879</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>115070</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136757</t>
+          <t>119302</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251827</t>
+          <t>242181</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11705</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6930</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19182</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14020</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22211</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,88%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12437</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7783</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>20492</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18460</t>
+          <t>16979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>33206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>220851</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>213374</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>225626</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,02%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>172878</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>164687</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>178220</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>236705</t>
+          <t>168944</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>228362</t>
+          <t>161176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>241359</t>
+          <t>173781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>409583</t>
+          <t>389795</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>398674</t>
+          <t>381018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>417580</t>
+          <t>397245</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>232556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>232556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>232556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186898</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>249142</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>249142</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>249142</t>
+          <t>181668</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>436040</t>
+          <t>414224</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>436040</t>
+          <t>414224</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>436040</t>
+          <t>414224</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12064</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6707</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19947</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,93%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4428</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15686</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>15566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>22280</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32442</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155083</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>147200</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>160440</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,78%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>178987</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>172301</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>183559</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,66%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>170423</t>
+          <t>145481</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162067</t>
+          <t>139107</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176050</t>
+          <t>149599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>349410</t>
+          <t>300563</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>339248</t>
+          <t>290652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>357292</t>
+          <t>307382</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>167147</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>187987</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183703</t>
+          <t>154673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371690</t>
+          <t>321820</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3113</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>13320</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10379</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5939</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17085</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6,25%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13760</t>
+          <t>16914</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17480</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26244</t>
+          <t>24960</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>160264</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>153288</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>163495</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,19%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>155737</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>149031</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>160177</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,75%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>170762</t>
+          <t>154612</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>164103</t>
+          <t>148257</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174443</t>
+          <t>159145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>326499</t>
+          <t>314876</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>317735</t>
+          <t>306819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>332563</t>
+          <t>321007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166608</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>166116</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177863</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>331779</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34294</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24835</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>46040</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>38849</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28474</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>50197</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37518</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>28520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49894</t>
+          <t>49187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>76367</t>
+          <t>72575</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61602</t>
+          <t>59739</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92702</t>
+          <t>89200</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>654896</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>643150</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>664355</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,4%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>867</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>617222</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>605874</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>627597</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>899</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>709947</t>
+          <t>582533</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>697571</t>
+          <t>571627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>720079</t>
+          <t>592294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1327169</t>
+          <t>1237429</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1310834</t>
+          <t>1220804</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1341934</t>
+          <t>1250265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>921</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
